--- a/data/Format=XLSX/Model=M10+/Floor=2/Location=West Hallway/Device=04/M10+_device04_11-10-2024 17:05:41.xlsx
+++ b/data/Format=XLSX/Model=M10+/Floor=2/Location=West Hallway/Device=04/M10+_device04_11-10-2024 17:05:41.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11110"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jack/Downloads/M10+_device04_11-10-2024 17:05:"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jack/Developer/Personal/Trellis Air Quality/trellis-aq/data/Format=XLSX/Model=M10+/Floor=2/Location=West Hallway/Device=04/M10+_device04_11-10-2024 17:05:"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAA54961-75C3-3549-B235-CE603F662BD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA30BF1-51CD-3440-9C16-F1CC36C6C11F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="880" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1360" uniqueCount="648">
   <si>
     <t>NO.</t>
   </si>
@@ -1435,6 +1435,12 @@
     <t>169</t>
   </si>
   <si>
+    <t>2024-11-10 15:00:00(+08:00)</t>
+  </si>
+  <si>
+    <t>123.6</t>
+  </si>
+  <si>
     <t>AQI</t>
   </si>
   <si>
@@ -1490,6 +1496,9 @@
   </si>
   <si>
     <t>226</t>
+  </si>
+  <si>
+    <t>199</t>
   </si>
   <si>
     <t>CO₂(ppm)</t>
@@ -2306,7 +2315,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H169"/>
+  <dimension ref="A1:H170"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.33203125" bestFit="1" customWidth="1"/>
@@ -2330,19 +2339,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -2359,13 +2368,13 @@
         <v>140</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>137</v>
@@ -2385,13 +2394,13 @@
         <v>82</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>134</v>
@@ -2411,13 +2420,13 @@
         <v>105</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>134</v>
@@ -2434,16 +2443,16 @@
         <v>14</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>129</v>
@@ -2460,16 +2469,16 @@
         <v>17</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>134</v>
@@ -2489,13 +2498,13 @@
         <v>407</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>132</v>
@@ -2515,13 +2524,13 @@
         <v>315</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>129</v>
@@ -2541,7 +2550,7 @@
         <v>190</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>140</v>
@@ -2567,13 +2576,13 @@
         <v>111</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>132</v>
@@ -2593,13 +2602,13 @@
         <v>99</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>134</v>
@@ -2619,13 +2628,13 @@
         <v>99</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>137</v>
@@ -2645,13 +2654,13 @@
         <v>99</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>137</v>
@@ -2671,13 +2680,13 @@
         <v>99</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>134</v>
@@ -2697,13 +2706,13 @@
         <v>82</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>134</v>
@@ -2723,13 +2732,13 @@
         <v>82</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>132</v>
@@ -2749,13 +2758,13 @@
         <v>76</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>132</v>
@@ -2775,7 +2784,7 @@
         <v>70</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>140</v>
@@ -2801,13 +2810,13 @@
         <v>70</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>123</v>
@@ -2827,13 +2836,13 @@
         <v>76</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>114</v>
@@ -2853,13 +2862,13 @@
         <v>114</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>114</v>
@@ -2879,13 +2888,13 @@
         <v>152</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>99</v>
@@ -2905,13 +2914,13 @@
         <v>158</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>85</v>
@@ -2931,13 +2940,13 @@
         <v>76</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>97</v>
@@ -2957,13 +2966,13 @@
         <v>146</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>120</v>
@@ -2983,13 +2992,13 @@
         <v>114</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>129</v>
@@ -3009,13 +3018,13 @@
         <v>79</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>132</v>
@@ -3035,13 +3044,13 @@
         <v>91</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>123</v>
@@ -3061,13 +3070,13 @@
         <v>73</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>97</v>
@@ -3087,13 +3096,13 @@
         <v>304</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>97</v>
@@ -3113,13 +3122,13 @@
         <v>390</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>99</v>
@@ -3139,7 +3148,7 @@
         <v>453</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>140</v>
@@ -3165,13 +3174,13 @@
         <v>255</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>102</v>
@@ -3191,7 +3200,7 @@
         <v>73</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>140</v>
@@ -3217,13 +3226,13 @@
         <v>54</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>99</v>
@@ -3243,13 +3252,13 @@
         <v>54</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>102</v>
@@ -3269,13 +3278,13 @@
         <v>52</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>99</v>
@@ -3295,13 +3304,13 @@
         <v>44</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>94</v>
@@ -3321,13 +3330,13 @@
         <v>35</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>88</v>
@@ -3347,13 +3356,13 @@
         <v>27</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>88</v>
@@ -3373,13 +3382,13 @@
         <v>24</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>88</v>
@@ -3399,13 +3408,13 @@
         <v>24</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>82</v>
@@ -3425,13 +3434,13 @@
         <v>21</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>82</v>
@@ -3448,16 +3457,16 @@
         <v>122</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>82</v>
@@ -3477,7 +3486,7 @@
         <v>232</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>140</v>
@@ -3503,13 +3512,13 @@
         <v>270</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>68</v>
@@ -3529,13 +3538,13 @@
         <v>264</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>65</v>
@@ -3555,13 +3564,13 @@
         <v>146</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>65</v>
@@ -3581,13 +3590,13 @@
         <v>57</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>73</v>
@@ -3607,13 +3616,13 @@
         <v>52</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>91</v>
@@ -3633,13 +3642,13 @@
         <v>33</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>102</v>
@@ -3659,13 +3668,13 @@
         <v>184</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>132</v>
@@ -3685,13 +3694,13 @@
         <v>445</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>137</v>
@@ -3711,13 +3720,13 @@
         <v>442</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>146</v>
@@ -3737,13 +3746,13 @@
         <v>459</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>158</v>
@@ -3760,16 +3769,16 @@
         <v>157</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>161</v>
@@ -3789,13 +3798,13 @@
         <v>155</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>155</v>
@@ -3815,13 +3824,13 @@
         <v>85</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>134</v>
@@ -3841,13 +3850,13 @@
         <v>73</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>117</v>
@@ -3867,13 +3876,13 @@
         <v>65</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>108</v>
@@ -3893,13 +3902,13 @@
         <v>65</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="H61" s="1" t="s">
         <v>102</v>
@@ -3919,13 +3928,13 @@
         <v>52</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>94</v>
@@ -3945,13 +3954,13 @@
         <v>44</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>88</v>
@@ -3971,13 +3980,13 @@
         <v>41</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>85</v>
@@ -3997,13 +4006,13 @@
         <v>37</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>85</v>
@@ -4023,13 +4032,13 @@
         <v>37</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>91</v>
@@ -4049,13 +4058,13 @@
         <v>50</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>91</v>
@@ -4075,13 +4084,13 @@
         <v>60</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>88</v>
@@ -4101,13 +4110,13 @@
         <v>73</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>82</v>
@@ -4127,13 +4136,13 @@
         <v>277</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>70</v>
@@ -4153,13 +4162,13 @@
         <v>425</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="H71" s="1" t="s">
         <v>63</v>
@@ -4179,13 +4188,13 @@
         <v>176</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>63</v>
@@ -4205,13 +4214,13 @@
         <v>192</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="H73" s="1" t="s">
         <v>60</v>
@@ -4231,13 +4240,13 @@
         <v>120</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>57</v>
@@ -4257,13 +4266,13 @@
         <v>275</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>52</v>
@@ -4283,13 +4292,13 @@
         <v>393</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>35</v>
@@ -4306,16 +4315,16 @@
         <v>215</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>33</v>
@@ -4332,16 +4341,16 @@
         <v>218</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="H78" s="1" t="s">
         <v>33</v>
@@ -4361,13 +4370,13 @@
         <v>439</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>33</v>
@@ -4384,16 +4393,16 @@
         <v>224</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>35</v>
@@ -4410,10 +4419,10 @@
         <v>227</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>140</v>
@@ -4439,13 +4448,13 @@
         <v>60</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="H82" s="1" t="s">
         <v>35</v>
@@ -4465,13 +4474,13 @@
         <v>44</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H83" s="1" t="s">
         <v>37</v>
@@ -4491,13 +4500,13 @@
         <v>30</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="H84" s="1" t="s">
         <v>37</v>
@@ -4517,13 +4526,13 @@
         <v>21</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="H85" s="1" t="s">
         <v>37</v>
@@ -4543,13 +4552,13 @@
         <v>18</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="H86" s="1" t="s">
         <v>37</v>
@@ -4569,13 +4578,13 @@
         <v>18</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="H87" s="1" t="s">
         <v>44</v>
@@ -4595,13 +4604,13 @@
         <v>21</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>50</v>
@@ -4621,13 +4630,13 @@
         <v>21</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>52</v>
@@ -4647,13 +4656,13 @@
         <v>24</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="H90" s="1" t="s">
         <v>57</v>
@@ -4673,13 +4682,13 @@
         <v>27</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="H91" s="1" t="s">
         <v>57</v>
@@ -4699,13 +4708,13 @@
         <v>245</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="H92" s="1" t="s">
         <v>63</v>
@@ -4725,13 +4734,13 @@
         <v>207</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="H93" s="1" t="s">
         <v>52</v>
@@ -4751,13 +4760,13 @@
         <v>102</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="H94" s="1" t="s">
         <v>39</v>
@@ -4777,13 +4786,13 @@
         <v>436</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>37</v>
@@ -4803,13 +4812,13 @@
         <v>187</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="H96" s="1" t="s">
         <v>39</v>
@@ -4829,13 +4838,13 @@
         <v>182</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="H97" s="1" t="s">
         <v>44</v>
@@ -4855,13 +4864,13 @@
         <v>85</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="H98" s="1" t="s">
         <v>52</v>
@@ -4881,13 +4890,13 @@
         <v>161</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>52</v>
@@ -4907,13 +4916,13 @@
         <v>79</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="H100" s="1" t="s">
         <v>70</v>
@@ -4933,13 +4942,13 @@
         <v>395</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="H101" s="1" t="s">
         <v>88</v>
@@ -4956,16 +4965,16 @@
         <v>282</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="H102" s="1" t="s">
         <v>91</v>
@@ -4985,13 +4994,13 @@
         <v>321</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="H103" s="1" t="s">
         <v>102</v>
@@ -5008,16 +5017,16 @@
         <v>288</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="H104" s="1" t="s">
         <v>108</v>
@@ -5034,16 +5043,16 @@
         <v>291</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="H105" s="1" t="s">
         <v>99</v>
@@ -5063,13 +5072,13 @@
         <v>143</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="H106" s="1" t="s">
         <v>91</v>
@@ -5089,13 +5098,13 @@
         <v>85</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="H107" s="1" t="s">
         <v>82</v>
@@ -5115,13 +5124,13 @@
         <v>57</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="H108" s="1" t="s">
         <v>79</v>
@@ -5141,13 +5150,13 @@
         <v>44</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="H109" s="1" t="s">
         <v>70</v>
@@ -5167,13 +5176,13 @@
         <v>41</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="H110" s="1" t="s">
         <v>54</v>
@@ -5193,13 +5202,13 @@
         <v>30</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="H111" s="1" t="s">
         <v>50</v>
@@ -5219,13 +5228,13 @@
         <v>21</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="H112" s="1" t="s">
         <v>47</v>
@@ -5245,13 +5254,13 @@
         <v>21</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="H113" s="1" t="s">
         <v>44</v>
@@ -5271,13 +5280,13 @@
         <v>15</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="H114" s="1" t="s">
         <v>44</v>
@@ -5297,13 +5306,13 @@
         <v>445</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="H115" s="1" t="s">
         <v>47</v>
@@ -5323,13 +5332,13 @@
         <v>164</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="H116" s="1" t="s">
         <v>47</v>
@@ -5349,13 +5358,13 @@
         <v>249</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="H117" s="1" t="s">
         <v>57</v>
@@ -5375,13 +5384,13 @@
         <v>184</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="H118" s="1" t="s">
         <v>47</v>
@@ -5401,13 +5410,13 @@
         <v>129</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="H119" s="1" t="s">
         <v>39</v>
@@ -5427,13 +5436,13 @@
         <v>219</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="H120" s="1" t="s">
         <v>39</v>
@@ -5453,13 +5462,13 @@
         <v>235</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="H121" s="1" t="s">
         <v>47</v>
@@ -5479,13 +5488,13 @@
         <v>126</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="H122" s="1" t="s">
         <v>52</v>
@@ -5505,13 +5514,13 @@
         <v>76</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="H123" s="1" t="s">
         <v>57</v>
@@ -5531,13 +5540,13 @@
         <v>169</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="H124" s="1" t="s">
         <v>47</v>
@@ -5557,13 +5566,13 @@
         <v>289</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="H125" s="1" t="s">
         <v>54</v>
@@ -5580,16 +5589,16 @@
         <v>348</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="H126" s="1" t="s">
         <v>63</v>
@@ -5609,13 +5618,13 @@
         <v>422</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="H127" s="1" t="s">
         <v>73</v>
@@ -5632,16 +5641,16 @@
         <v>354</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="H128" s="1" t="s">
         <v>88</v>
@@ -5661,13 +5670,13 @@
         <v>355</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="H129" s="1" t="s">
         <v>88</v>
@@ -5687,13 +5696,13 @@
         <v>169</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="H130" s="1" t="s">
         <v>73</v>
@@ -5713,13 +5722,13 @@
         <v>134</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="H131" s="1" t="s">
         <v>63</v>
@@ -5739,13 +5748,13 @@
         <v>82</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="H132" s="1" t="s">
         <v>54</v>
@@ -5765,13 +5774,13 @@
         <v>88</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="H133" s="1" t="s">
         <v>54</v>
@@ -5791,13 +5800,13 @@
         <v>70</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="H134" s="1" t="s">
         <v>54</v>
@@ -5817,13 +5826,13 @@
         <v>52</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="H135" s="1" t="s">
         <v>57</v>
@@ -5843,13 +5852,13 @@
         <v>39</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H136" s="1" t="s">
         <v>63</v>
@@ -5869,13 +5878,13 @@
         <v>39</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="H137" s="1" t="s">
         <v>68</v>
@@ -5895,13 +5904,13 @@
         <v>129</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="H138" s="1" t="s">
         <v>73</v>
@@ -5921,13 +5930,13 @@
         <v>57</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="H139" s="1" t="s">
         <v>63</v>
@@ -5947,13 +5956,13 @@
         <v>63</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="H140" s="1" t="s">
         <v>73</v>
@@ -5973,13 +5982,13 @@
         <v>470</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="H141" s="1" t="s">
         <v>73</v>
@@ -5999,13 +6008,13 @@
         <v>174</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="H142" s="1" t="s">
         <v>54</v>
@@ -6025,13 +6034,13 @@
         <v>70</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="H143" s="1" t="s">
         <v>50</v>
@@ -6051,13 +6060,13 @@
         <v>210</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="H144" s="1" t="s">
         <v>50</v>
@@ -6077,13 +6086,13 @@
         <v>425</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="H145" s="1" t="s">
         <v>47</v>
@@ -6103,13 +6112,13 @@
         <v>450</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="H146" s="1" t="s">
         <v>60</v>
@@ -6129,13 +6138,13 @@
         <v>210</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="H147" s="1" t="s">
         <v>65</v>
@@ -6155,13 +6164,13 @@
         <v>207</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="H148" s="1" t="s">
         <v>68</v>
@@ -6181,13 +6190,13 @@
         <v>428</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="H149" s="1" t="s">
         <v>60</v>
@@ -6204,16 +6213,16 @@
         <v>415</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="H150" s="1" t="s">
         <v>63</v>
@@ -6230,16 +6239,16 @@
         <v>418</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="H151" s="1" t="s">
         <v>102</v>
@@ -6256,10 +6265,10 @@
         <v>421</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>140</v>
@@ -6282,16 +6291,16 @@
         <v>424</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="H153" s="1" t="s">
         <v>123</v>
@@ -6311,13 +6320,13 @@
         <v>292</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="H154" s="1" t="s">
         <v>120</v>
@@ -6337,13 +6346,13 @@
         <v>210</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="H155" s="1" t="s">
         <v>123</v>
@@ -6363,13 +6372,13 @@
         <v>198</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="H156" s="1" t="s">
         <v>123</v>
@@ -6389,13 +6398,13 @@
         <v>182</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="H157" s="1" t="s">
         <v>111</v>
@@ -6415,13 +6424,13 @@
         <v>172</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="H158" s="1" t="s">
         <v>91</v>
@@ -6441,13 +6450,13 @@
         <v>169</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="H159" s="1" t="s">
         <v>85</v>
@@ -6467,13 +6476,13 @@
         <v>158</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="H160" s="1" t="s">
         <v>85</v>
@@ -6493,13 +6502,13 @@
         <v>149</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="H161" s="1" t="s">
         <v>85</v>
@@ -6519,13 +6528,13 @@
         <v>146</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="H162" s="1" t="s">
         <v>79</v>
@@ -6545,13 +6554,13 @@
         <v>190</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="H163" s="1" t="s">
         <v>82</v>
@@ -6568,16 +6577,16 @@
         <v>455</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="H164" s="1" t="s">
         <v>73</v>
@@ -6594,16 +6603,16 @@
         <v>458</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="H165" s="1" t="s">
         <v>68</v>
@@ -6620,16 +6629,16 @@
         <v>461</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="H166" s="1" t="s">
         <v>63</v>
@@ -6649,13 +6658,13 @@
         <v>192</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="H167" s="1" t="s">
         <v>65</v>
@@ -6675,13 +6684,13 @@
         <v>207</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="H168" s="1" t="s">
         <v>91</v>
@@ -6701,16 +6710,42 @@
         <v>428</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="H169" s="1" t="s">
         <v>105</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A170" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G170" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="H170" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
